--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.6071463761354</v>
+        <v>7.898661286122003</v>
       </c>
       <c r="D2" t="n">
-        <v>49.23339660387746</v>
+        <v>8.000426948130087</v>
       </c>
       <c r="E2" t="n">
-        <v>11.50046745716715</v>
+        <v>1.868825961789661</v>
       </c>
       <c r="F2" t="n">
-        <v>11.73353709689856</v>
+        <v>1.906699778246015</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.14757443129162</v>
+        <v>8.311480845084889</v>
       </c>
       <c r="D3" t="n">
-        <v>51.81384059338691</v>
+        <v>8.419749096425374</v>
       </c>
       <c r="E3" t="n">
-        <v>11.50046745716715</v>
+        <v>1.868825961789661</v>
       </c>
       <c r="F3" t="n">
-        <v>11.73353709689856</v>
+        <v>1.906699778246015</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>62.97573431724159</v>
+        <v>10.23355682655176</v>
       </c>
       <c r="D4" t="n">
-        <v>63.62365158480328</v>
+        <v>10.33884338253053</v>
       </c>
       <c r="E4" t="n">
-        <v>11.50046745716715</v>
+        <v>1.868825961789661</v>
       </c>
       <c r="F4" t="n">
-        <v>11.73353709689856</v>
+        <v>1.906699778246015</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.07122033437184</v>
+        <v>4.236573304335425</v>
       </c>
       <c r="D5" t="n">
-        <v>26.21001463449005</v>
+        <v>4.259127378104633</v>
       </c>
       <c r="E5" t="n">
-        <v>11.50046745716715</v>
+        <v>1.868825961789661</v>
       </c>
       <c r="F5" t="n">
-        <v>11.73353709689856</v>
+        <v>1.906699778246015</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>47.03655411857853</v>
+        <v>7.643440044269012</v>
       </c>
       <c r="D6" t="n">
-        <v>46.37512170505563</v>
+        <v>7.535957277071541</v>
       </c>
       <c r="E6" t="n">
-        <v>11.50046745716715</v>
+        <v>1.868825961789661</v>
       </c>
       <c r="F6" t="n">
-        <v>11.73353709689856</v>
+        <v>1.906699778246015</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.32810314830497</v>
+        <v>6.065816761599558</v>
       </c>
       <c r="D7" t="n">
-        <v>37.06164822998287</v>
+        <v>6.022517837372217</v>
       </c>
       <c r="E7" t="n">
-        <v>11.50046745716715</v>
+        <v>1.868825961789661</v>
       </c>
       <c r="F7" t="n">
-        <v>11.73353709689856</v>
+        <v>1.906699778246015</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
